--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="180">
   <si>
     <t>Sezione</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Generalità Sposa</t>
@@ -604,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -1952,19 +1958,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1975,19 +1981,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1998,19 +2004,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -2021,19 +2027,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2044,19 +2050,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2067,19 +2073,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2090,19 +2096,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2113,19 +2119,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2136,19 +2142,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2159,19 +2165,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2182,19 +2188,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2205,19 +2211,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2228,19 +2234,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2251,19 +2257,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2274,19 +2280,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2297,19 +2303,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2320,19 +2326,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2343,19 +2349,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2366,19 +2372,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2389,19 +2395,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2412,19 +2418,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2435,19 +2441,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2458,19 +2464,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2481,19 +2487,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2504,19 +2510,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2527,19 +2533,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2550,19 +2556,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2573,19 +2579,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2596,19 +2602,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2619,19 +2625,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2645,16 +2651,16 @@
         <v>125</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2668,16 +2674,16 @@
         <v>125</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2688,19 +2694,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2711,19 +2717,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2734,19 +2740,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2757,19 +2763,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2780,19 +2786,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2803,19 +2809,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2826,19 +2832,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2849,19 +2855,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2872,19 +2878,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2895,19 +2901,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2918,19 +2924,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2941,19 +2947,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2964,19 +2970,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2987,19 +2993,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3010,19 +3016,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3033,19 +3039,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3056,19 +3062,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3079,19 +3085,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3102,19 +3108,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3125,19 +3131,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3148,19 +3154,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3171,19 +3177,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3194,19 +3200,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3217,19 +3223,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3243,19 +3249,19 @@
         <v>153</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E115" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>29</v>
@@ -3266,16 +3272,16 @@
         <v>153</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3286,22 +3292,22 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>29</v>
@@ -3309,19 +3315,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3332,22 +3338,22 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>29</v>
@@ -3355,22 +3361,22 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>29</v>
@@ -3378,22 +3384,22 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>29</v>
@@ -3401,22 +3407,22 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>29</v>
@@ -3424,19 +3430,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3447,22 +3453,22 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>29</v>
@@ -3470,19 +3476,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3493,19 +3499,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>22</v>
@@ -3516,22 +3522,22 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>29</v>
@@ -3539,22 +3545,22 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>29</v>
@@ -3562,22 +3568,22 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>29</v>
@@ -3585,22 +3591,22 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>29</v>
@@ -3608,22 +3614,22 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>29</v>
@@ -3631,22 +3637,22 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>29</v>
@@ -3654,19 +3660,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>22</v>
@@ -3677,19 +3683,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3700,19 +3706,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>22</v>
@@ -3723,19 +3729,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3746,19 +3752,19 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>22</v>
@@ -3769,22 +3775,22 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>29</v>
@@ -3792,22 +3798,22 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>29</v>
@@ -3815,22 +3821,22 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>29</v>
@@ -3838,22 +3844,22 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E141" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>29</v>
@@ -3861,19 +3867,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -3884,22 +3890,22 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>29</v>
@@ -3907,19 +3913,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
@@ -3930,19 +3936,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
@@ -3953,19 +3959,19 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
@@ -3976,19 +3982,19 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -3999,19 +4005,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
@@ -4022,19 +4028,19 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
@@ -4045,19 +4051,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
@@ -4068,24 +4074,70 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="C153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F151" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G151" s="2" t="s">
+      <c r="F153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="2" t="s">
         <v>29</v>
       </c>
     </row>
